--- a/DatasetMaestro.xlsx
+++ b/DatasetMaestro.xlsx
@@ -1,40 +1,190 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos_Pacientes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos_Pacientes" sheetId="1" r:id="rId1"/>
+    <sheet name="Estadisticas_Globales" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="46">
+  <si>
+    <t>CodeID</t>
+  </si>
+  <si>
+    <t>TUG_duracion_seg</t>
+  </si>
+  <si>
+    <t>TUG_Left_pasos</t>
+  </si>
+  <si>
+    <t>TUG_Left_cadencia</t>
+  </si>
+  <si>
+    <t>TUG_Left_apoyo_prc</t>
+  </si>
+  <si>
+    <t>TUG_Left_balanceo_prc</t>
+  </si>
+  <si>
+    <t>TUG_Right_pasos</t>
+  </si>
+  <si>
+    <t>TUG_Right_cadencia</t>
+  </si>
+  <si>
+    <t>TUG_Right_apoyo_prc</t>
+  </si>
+  <si>
+    <t>TUG_Right_balanceo_prc</t>
+  </si>
+  <si>
+    <t>6MWT_duracion_seg</t>
+  </si>
+  <si>
+    <t>6MWT_Left_pasos</t>
+  </si>
+  <si>
+    <t>6MWT_Left_cadencia</t>
+  </si>
+  <si>
+    <t>6MWT_Left_apoyo_prc</t>
+  </si>
+  <si>
+    <t>6MWT_Left_balanceo_prc</t>
+  </si>
+  <si>
+    <t>6MWT_Left_decaimiento_prc</t>
+  </si>
+  <si>
+    <t>6MWT_Right_pasos</t>
+  </si>
+  <si>
+    <t>6MWT_Right_cadencia</t>
+  </si>
+  <si>
+    <t>6MWT_Right_apoyo_prc</t>
+  </si>
+  <si>
+    <t>6MWT_Right_balanceo_prc</t>
+  </si>
+  <si>
+    <t>6MWT_Right_decaimiento_prc</t>
+  </si>
+  <si>
+    <t>T25FW_duracion_seg</t>
+  </si>
+  <si>
+    <t>T25FW_Left_pasos</t>
+  </si>
+  <si>
+    <t>T25FW_Left_cadencia</t>
+  </si>
+  <si>
+    <t>T25FW_Left_apoyo_prc</t>
+  </si>
+  <si>
+    <t>T25FW_Left_balanceo_prc</t>
+  </si>
+  <si>
+    <t>T25FW_Right_pasos</t>
+  </si>
+  <si>
+    <t>T25FW_Right_cadencia</t>
+  </si>
+  <si>
+    <t>T25FW_Right_apoyo_prc</t>
+  </si>
+  <si>
+    <t>T25FW_Right_balanceo_prc</t>
+  </si>
+  <si>
+    <t>AMIR-48</t>
+  </si>
+  <si>
+    <t>SENSORIA-57</t>
+  </si>
+  <si>
+    <t>47046344M-104</t>
+  </si>
+  <si>
+    <t>01912299X-118</t>
+  </si>
+  <si>
+    <t>PLMHUG001-29</t>
+  </si>
+  <si>
+    <t>SOMHUG003-31</t>
+  </si>
+  <si>
+    <t>RHRHUG004-1</t>
+  </si>
+  <si>
+    <t>RSBHUG005-11</t>
+  </si>
+  <si>
+    <t>RSBHUGOO5-11</t>
+  </si>
+  <si>
+    <t>53471345W-118</t>
+  </si>
+  <si>
+    <t>EPGHUG006-25</t>
+  </si>
+  <si>
+    <t>EMMHUG008-0</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +192,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,106 +509,1582 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AD13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>CodeID</t>
-        </is>
+    <row r="1" spans="1:30">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AMIR-48</t>
-        </is>
+    <row r="2" spans="1:30">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SENSORIA-57</t>
-        </is>
+    <row r="3" spans="1:30">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" t="s">
+        <v>42</v>
+      </c>
+      <c r="S3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>47046344M-104</t>
-        </is>
+    <row r="4" spans="1:30">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O4" t="s">
+        <v>42</v>
+      </c>
+      <c r="P4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R4" t="s">
+        <v>42</v>
+      </c>
+      <c r="S4" t="s">
+        <v>42</v>
+      </c>
+      <c r="T4" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" t="s">
+        <v>42</v>
+      </c>
+      <c r="V4" t="s">
+        <v>42</v>
+      </c>
+      <c r="W4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>01912299X-118</t>
-        </is>
+    <row r="5" spans="1:30">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5">
+        <v>10.07</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>12.24</v>
+      </c>
+      <c r="E5">
+        <v>48.37</v>
+      </c>
+      <c r="F5">
+        <v>51.63</v>
+      </c>
+      <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>95.73999999999999</v>
+      </c>
+      <c r="I5">
+        <v>54.47</v>
+      </c>
+      <c r="J5">
+        <v>45.53</v>
+      </c>
+      <c r="K5">
+        <v>360</v>
+      </c>
+      <c r="L5">
+        <v>37</v>
+      </c>
+      <c r="M5">
+        <v>30.53</v>
+      </c>
+      <c r="N5">
+        <v>54.74</v>
+      </c>
+      <c r="O5">
+        <v>45.26</v>
+      </c>
+      <c r="P5">
+        <v>47.33</v>
+      </c>
+      <c r="Q5">
+        <v>93</v>
+      </c>
+      <c r="R5">
+        <v>36.89</v>
+      </c>
+      <c r="S5">
+        <v>55.14</v>
+      </c>
+      <c r="T5">
+        <v>44.86</v>
+      </c>
+      <c r="U5">
+        <v>54.32</v>
+      </c>
+      <c r="V5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W5" t="s">
+        <v>42</v>
+      </c>
+      <c r="X5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PLMHUG001-29</t>
-        </is>
+    <row r="6" spans="1:30">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6">
+        <v>5.33</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>50.57</v>
+      </c>
+      <c r="F6">
+        <v>49.43</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>54.51</v>
+      </c>
+      <c r="J6">
+        <v>45.49</v>
+      </c>
+      <c r="K6">
+        <v>360.02</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>71.92</v>
+      </c>
+      <c r="O6">
+        <v>28.08</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>46.43</v>
+      </c>
+      <c r="T6">
+        <v>53.57</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>4.4</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>21.13</v>
+      </c>
+      <c r="Y6">
+        <v>75</v>
+      </c>
+      <c r="Z6">
+        <v>25</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>31.94</v>
+      </c>
+      <c r="AD6">
+        <v>68.06</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SOMHUG003-31</t>
-        </is>
+    <row r="7" spans="1:30">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7">
+        <v>6.17</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>44.92</v>
+      </c>
+      <c r="F7">
+        <v>55.08</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>76.70999999999999</v>
+      </c>
+      <c r="J7">
+        <v>23.29</v>
+      </c>
+      <c r="K7">
+        <v>360.01</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0.34</v>
+      </c>
+      <c r="N7">
+        <v>66.37</v>
+      </c>
+      <c r="O7">
+        <v>33.63</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>38.82</v>
+      </c>
+      <c r="T7">
+        <v>61.18</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>6.59</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>46.79</v>
+      </c>
+      <c r="Z7">
+        <v>53.21</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>30.46</v>
+      </c>
+      <c r="AD7">
+        <v>69.54000000000001</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RHRHUG004-1</t>
-        </is>
+    <row r="8" spans="1:30">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8">
+        <v>360.02</v>
+      </c>
+      <c r="L8">
+        <v>23</v>
+      </c>
+      <c r="M8">
+        <v>5.09</v>
+      </c>
+      <c r="N8">
+        <v>57.23</v>
+      </c>
+      <c r="O8">
+        <v>42.77</v>
+      </c>
+      <c r="P8">
+        <v>21.97</v>
+      </c>
+      <c r="Q8">
+        <v>2</v>
+      </c>
+      <c r="R8">
+        <v>0.9</v>
+      </c>
+      <c r="S8">
+        <v>58.14</v>
+      </c>
+      <c r="T8">
+        <v>41.86</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
+        <v>42</v>
+      </c>
+      <c r="W8" t="s">
+        <v>42</v>
+      </c>
+      <c r="X8" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RSBHUG005-11</t>
-        </is>
+    <row r="9" spans="1:30">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9" t="s">
+        <v>42</v>
+      </c>
+      <c r="O9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>42</v>
+      </c>
+      <c r="R9" t="s">
+        <v>42</v>
+      </c>
+      <c r="S9" t="s">
+        <v>42</v>
+      </c>
+      <c r="T9" t="s">
+        <v>42</v>
+      </c>
+      <c r="U9" t="s">
+        <v>42</v>
+      </c>
+      <c r="V9" t="s">
+        <v>42</v>
+      </c>
+      <c r="W9" t="s">
+        <v>42</v>
+      </c>
+      <c r="X9" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RSBHUGOO5-11</t>
-        </is>
+    <row r="10" spans="1:30">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10">
+        <v>360</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>50.07</v>
+      </c>
+      <c r="O10">
+        <v>49.93</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>67.36</v>
+      </c>
+      <c r="T10">
+        <v>32.64</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
+        <v>42</v>
+      </c>
+      <c r="W10" t="s">
+        <v>42</v>
+      </c>
+      <c r="X10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>53471345W-118</t>
-        </is>
+    <row r="11" spans="1:30">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L11" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" t="s">
+        <v>42</v>
+      </c>
+      <c r="N11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O11" t="s">
+        <v>42</v>
+      </c>
+      <c r="P11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>42</v>
+      </c>
+      <c r="R11" t="s">
+        <v>42</v>
+      </c>
+      <c r="S11" t="s">
+        <v>42</v>
+      </c>
+      <c r="T11" t="s">
+        <v>42</v>
+      </c>
+      <c r="U11" t="s">
+        <v>42</v>
+      </c>
+      <c r="V11" t="s">
+        <v>42</v>
+      </c>
+      <c r="W11" t="s">
+        <v>42</v>
+      </c>
+      <c r="X11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>EPGHUG006-25</t>
-        </is>
+    <row r="12" spans="1:30">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12">
+        <v>7.28</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>43.19</v>
+      </c>
+      <c r="F12">
+        <v>56.81</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>66.81</v>
+      </c>
+      <c r="J12">
+        <v>33.19</v>
+      </c>
+      <c r="K12">
+        <v>360.01</v>
+      </c>
+      <c r="L12">
+        <v>7</v>
+      </c>
+      <c r="M12">
+        <v>1.28</v>
+      </c>
+      <c r="N12">
+        <v>23.62</v>
+      </c>
+      <c r="O12">
+        <v>76.38</v>
+      </c>
+      <c r="P12">
+        <v>100</v>
+      </c>
+      <c r="Q12">
+        <v>14</v>
+      </c>
+      <c r="R12">
+        <v>2.51</v>
+      </c>
+      <c r="S12">
+        <v>23.81</v>
+      </c>
+      <c r="T12">
+        <v>76.19</v>
+      </c>
+      <c r="U12">
+        <v>100</v>
+      </c>
+      <c r="V12">
+        <v>6.73</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>51.1</v>
+      </c>
+      <c r="Z12">
+        <v>48.9</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>52.04</v>
+      </c>
+      <c r="AD12">
+        <v>47.96</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>EMMHUG008-0</t>
-        </is>
+    <row r="13" spans="1:30">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13">
+        <v>5.57</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>41.83</v>
+      </c>
+      <c r="F13">
+        <v>58.17</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>43.8</v>
+      </c>
+      <c r="I13">
+        <v>44.53</v>
+      </c>
+      <c r="J13">
+        <v>55.47</v>
+      </c>
+      <c r="K13">
+        <v>360.01</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>75.01000000000001</v>
+      </c>
+      <c r="O13">
+        <v>24.99</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>72.53</v>
+      </c>
+      <c r="T13">
+        <v>27.47</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>5.3</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>87.29000000000001</v>
+      </c>
+      <c r="Z13">
+        <v>12.71</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>15.23</v>
+      </c>
+      <c r="AD13">
+        <v>84.77</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AD4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:30">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30">
+      <c r="A2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2">
+        <v>6.884</v>
+      </c>
+      <c r="C2">
+        <v>0.2</v>
+      </c>
+      <c r="D2">
+        <v>2.448</v>
+      </c>
+      <c r="E2">
+        <v>45.776</v>
+      </c>
+      <c r="F2">
+        <v>54.224</v>
+      </c>
+      <c r="G2">
+        <v>3.6</v>
+      </c>
+      <c r="H2">
+        <v>27.908</v>
+      </c>
+      <c r="I2">
+        <v>59.40599999999999</v>
+      </c>
+      <c r="J2">
+        <v>40.594</v>
+      </c>
+      <c r="K2">
+        <v>360.0099999999999</v>
+      </c>
+      <c r="L2">
+        <v>9.714285714285714</v>
+      </c>
+      <c r="M2">
+        <v>5.32</v>
+      </c>
+      <c r="N2">
+        <v>56.99428571428572</v>
+      </c>
+      <c r="O2">
+        <v>43.00571428571429</v>
+      </c>
+      <c r="P2">
+        <v>24.18571428571429</v>
+      </c>
+      <c r="Q2">
+        <v>15.57142857142857</v>
+      </c>
+      <c r="R2">
+        <v>5.757142857142857</v>
+      </c>
+      <c r="S2">
+        <v>51.74714285714286</v>
+      </c>
+      <c r="T2">
+        <v>48.25285714285714</v>
+      </c>
+      <c r="U2">
+        <v>22.04571428571429</v>
+      </c>
+      <c r="V2">
+        <v>5.755</v>
+      </c>
+      <c r="W2">
+        <v>0.25</v>
+      </c>
+      <c r="X2">
+        <v>5.2825</v>
+      </c>
+      <c r="Y2">
+        <v>65.045</v>
+      </c>
+      <c r="Z2">
+        <v>34.95500000000001</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>32.4175</v>
+      </c>
+      <c r="AD2">
+        <v>67.58250000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3">
+        <v>6.17</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>44.92</v>
+      </c>
+      <c r="F3">
+        <v>55.08</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>54.51</v>
+      </c>
+      <c r="J3">
+        <v>45.49</v>
+      </c>
+      <c r="K3">
+        <v>360.01</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0.34</v>
+      </c>
+      <c r="N3">
+        <v>57.23</v>
+      </c>
+      <c r="O3">
+        <v>42.77</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>55.14</v>
+      </c>
+      <c r="T3">
+        <v>44.86</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>5.945</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>63.05</v>
+      </c>
+      <c r="Z3">
+        <v>36.95</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>31.2</v>
+      </c>
+      <c r="AD3">
+        <v>68.80000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
+      <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4">
+        <v>1.933825224781185</v>
+      </c>
+      <c r="C4">
+        <v>0.447213595499958</v>
+      </c>
+      <c r="D4">
+        <v>5.473894408919485</v>
+      </c>
+      <c r="E4">
+        <v>3.629818177264531</v>
+      </c>
+      <c r="F4">
+        <v>3.629818177264531</v>
+      </c>
+      <c r="G4">
+        <v>6.50384501660364</v>
+      </c>
+      <c r="H4">
+        <v>42.39783390693444</v>
+      </c>
+      <c r="I4">
+        <v>12.48877415921995</v>
+      </c>
+      <c r="J4">
+        <v>12.48877415921995</v>
+      </c>
+      <c r="K4">
+        <v>0.008164965809269835</v>
+      </c>
+      <c r="L4">
+        <v>14.6482568441241</v>
+      </c>
+      <c r="M4">
+        <v>11.26666321498961</v>
+      </c>
+      <c r="N4">
+        <v>17.33095963600291</v>
+      </c>
+      <c r="O4">
+        <v>17.3309596360029</v>
+      </c>
+      <c r="P4">
+        <v>37.92134045500979</v>
+      </c>
+      <c r="Q4">
+        <v>34.52466337203566</v>
+      </c>
+      <c r="R4">
+        <v>13.75965929118609</v>
+      </c>
+      <c r="S4">
+        <v>16.85198080769312</v>
+      </c>
+      <c r="T4">
+        <v>16.85198080769312</v>
+      </c>
+      <c r="U4">
+        <v>39.8927056227672</v>
+      </c>
+      <c r="V4">
+        <v>1.109188892840169</v>
+      </c>
+      <c r="W4">
+        <v>0.5</v>
+      </c>
+      <c r="X4">
+        <v>10.565</v>
+      </c>
+      <c r="Y4">
+        <v>19.33606388763408</v>
+      </c>
+      <c r="Z4">
+        <v>19.33606388763408</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>15.1053243924121</v>
+      </c>
+      <c r="AD4">
+        <v>15.1053243924121</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>